--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.54547098459776</v>
+        <v>10.65113903499714</v>
       </c>
       <c r="D2" t="n">
-        <v>62.43557726180863</v>
+        <v>10.1457813050439</v>
       </c>
       <c r="E2" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F2" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.02512495872727</v>
+        <v>9.104082805793182</v>
       </c>
       <c r="D3" t="n">
-        <v>59.12903893163476</v>
+        <v>9.608468826390649</v>
       </c>
       <c r="E3" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F3" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.6939129893574</v>
+        <v>10.18776086077058</v>
       </c>
       <c r="D4" t="n">
-        <v>59.85278455941024</v>
+        <v>9.726077490904164</v>
       </c>
       <c r="E4" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F4" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.36769209246674</v>
+        <v>8.184749965025846</v>
       </c>
       <c r="D5" t="n">
-        <v>77.53164077172261</v>
+        <v>12.59889162540492</v>
       </c>
       <c r="E5" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F5" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.40921518572337</v>
+        <v>3.641497467680047</v>
       </c>
       <c r="D6" t="n">
-        <v>49.20327310334057</v>
+        <v>7.995531879292843</v>
       </c>
       <c r="E6" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F6" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.36635814608329</v>
+        <v>8.997033198738535</v>
       </c>
       <c r="D7" t="n">
-        <v>54.62090634927932</v>
+        <v>8.87589728175789</v>
       </c>
       <c r="E7" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F7" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.21308283729654</v>
+        <v>5.722125961060688</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9174858746179</v>
+        <v>5.83659145462541</v>
       </c>
       <c r="E8" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F8" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.47292517184195</v>
+        <v>3.651850340424318</v>
       </c>
       <c r="D9" t="n">
-        <v>22.74704184863878</v>
+        <v>3.696394300403801</v>
       </c>
       <c r="E9" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F9" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49227843083898</v>
+        <v>3.654995245011334</v>
       </c>
       <c r="D10" t="n">
-        <v>21.61998063536146</v>
+        <v>3.513246853246237</v>
       </c>
       <c r="E10" t="n">
-        <v>16.98394298926289</v>
+        <v>2.75989073575522</v>
       </c>
       <c r="F10" t="n">
-        <v>17.81432166581974</v>
+        <v>2.894827270695708</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
